--- a/data/VN_order_simulation(test).xlsx
+++ b/data/VN_order_simulation(test).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA27464E-AE89-446B-9217-8429C7FCC688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5203C4-B67F-4F15-921B-97841D26FEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9C8133E3-E864-46F0-B892-95CA47D890F9}"/>
   </bookViews>
@@ -170,7 +170,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -180,6 +180,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -519,7 +520,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="83.109375" customWidth="1"/>
+    <col min="1" max="1" width="116.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
@@ -534,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC87C225-7C42-476D-B5F5-C80092089EF3}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
@@ -545,7 +546,7 @@
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -588,8 +589,12 @@
         <f>TEXT(E2 / 86400, "[h]:mm")</f>
         <v>81:43</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="7">
+        <f>1-F2</f>
+        <v>0.27942671540139297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -612,8 +617,12 @@
         <f t="shared" ref="H3:H9" si="0">TEXT(E3 / 86400, "[h]:mm")</f>
         <v>71:27</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I9" si="1">1-F3</f>
+        <v>0.35194915560092399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -636,8 +645,12 @@
         <f t="shared" si="0"/>
         <v>84:01</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="7">
+        <f t="shared" si="1"/>
+        <v>0.27662276250402795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -660,8 +673,12 @@
         <f t="shared" si="0"/>
         <v>85:33</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.23142684233814703</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -684,8 +701,12 @@
         <f t="shared" si="0"/>
         <v>82:52</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="7">
+        <f t="shared" si="1"/>
+        <v>0.24915368764592405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -708,8 +729,12 @@
         <f t="shared" si="0"/>
         <v>85:41</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="7">
+        <f t="shared" si="1"/>
+        <v>0.23451573804155201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -732,8 +757,12 @@
         <f t="shared" si="0"/>
         <v>88:22</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="7">
+        <f t="shared" si="1"/>
+        <v>0.22625192469376998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -756,8 +785,12 @@
         <f t="shared" si="0"/>
         <v>83:30</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="7">
+        <f t="shared" si="1"/>
+        <v>0.26706912405716898</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" s="6">
         <f>AVERAGE(C2:C9)</f>
         <v>327023.875</v>
